--- a/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/01_Avaliacao_do_Governo.xlsx
+++ b/ENTREGA_FINAL/RESULTADOS_ATUAIS/Modelo_A_Baseline_Oficial/01_Avaliacao_do_Governo.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1217"/>
+  <dimension ref="A1:D1218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17483,6 +17483,20 @@
       </c>
       <c r="D1217" t="n">
         <v>47.65242156082476</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>38.86227681270186</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>14.27695110666464</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>46.61869819018781</v>
       </c>
     </row>
   </sheetData>
@@ -17496,7 +17510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1217"/>
+  <dimension ref="A1:D1218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34543,6 +34557,20 @@
       </c>
       <c r="D1217" t="n">
         <v>46.67679659756904</v>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>37.8404072623488</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>13.55717192082162</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>45.57615757366666</v>
       </c>
     </row>
   </sheetData>
@@ -34556,7 +34584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1217"/>
+  <dimension ref="A1:D1218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51605,6 +51633,20 @@
         <v>48.62804652408048</v>
       </c>
     </row>
+    <row r="1218">
+      <c r="A1218" s="3" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B1218" t="n">
+        <v>39.88414636305493</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>14.99673029250766</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>47.66123880670897</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
